--- a/tasks/finalpool/yt-ml-repos-github-notion-excel-email/groundtruth_workspace/ML_Research_Tracker.xlsx
+++ b/tasks/finalpool/yt-ml-repos-github-notion-excel-email/groundtruth_workspace/ML_Research_Tracker.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Flash Attention - Faster Transformer Training</t>
+          <t>Flash Attention - Faster Transformer Training Explained</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stable Diffusion - Open Source Image Generation</t>
+          <t>Stable Diffusion - Open Source Image Generation Deep Dive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mixtral - Mixture of Experts Explained</t>
+          <t>Mixtral - Mixture of Experts Architecture Explained</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FlashAttention-2: Faster Attention with Better Parallelism</t>
+          <t>FlashAttention-2: Faster Attention with Better Parallelism and Work Partitioning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
